--- a/data/trans_dic/Q25_A_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,72; 27,37</t>
+          <t>13,25; 27,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,03; 31,48</t>
+          <t>18,6; 31,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,19; 25,41</t>
+          <t>11,26; 25,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 17,33</t>
+          <t>5,78; 17,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,46; 54,56</t>
+          <t>23,82; 52,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,56; 50,85</t>
+          <t>28,67; 50,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,03; 50,97</t>
+          <t>26,23; 49,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,24; 29,13</t>
+          <t>11,7; 29,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,6; 31,04</t>
+          <t>18,34; 31,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,72; 34,34</t>
+          <t>23,06; 34,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,77; 29,86</t>
+          <t>18,53; 30,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,13; 19,12</t>
+          <t>9,1; 18,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,28; 32,56</t>
+          <t>19,23; 32,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,38; 33,43</t>
+          <t>21,73; 32,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,37; 29,16</t>
+          <t>16,32; 27,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 92,13</t>
+          <t>13,91; 92,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 45,67</t>
+          <t>23,28; 44,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,36; 53,1</t>
+          <t>32,49; 52,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,33; 39,08</t>
+          <t>21,77; 40,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,15; 41,11</t>
+          <t>23,86; 41,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,8; 33,26</t>
+          <t>22,09; 33,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,13; 35,85</t>
+          <t>26,11; 36,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,67; 29,52</t>
+          <t>19,73; 29,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 87,18</t>
+          <t>19,84; 87,91</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,05; 35,91</t>
+          <t>20,0; 36,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,97; 36,34</t>
+          <t>22,2; 36,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,08; 35,19</t>
+          <t>20,48; 36,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 26,29</t>
+          <t>11,8; 26,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,31; 63,18</t>
+          <t>33,07; 65,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,96; 48,34</t>
+          <t>27,81; 47,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,85; 36,5</t>
+          <t>17,42; 36,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,85; 37,97</t>
+          <t>16,4; 36,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,82; 39,91</t>
+          <t>25,92; 39,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,74; 38,45</t>
+          <t>27,01; 38,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,8; 33,91</t>
+          <t>21,28; 33,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,4; 27,2</t>
+          <t>15,17; 26,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,42; 28,41</t>
+          <t>16,06; 27,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,8; 33,98</t>
+          <t>21,21; 33,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,78; 32,49</t>
+          <t>20,1; 32,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,28; 22,47</t>
+          <t>11,69; 22,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,38; 47,47</t>
+          <t>27,63; 48,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,36; 37,9</t>
+          <t>20,0; 38,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,46; 41,84</t>
+          <t>25,05; 41,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,21; 33,69</t>
+          <t>19,4; 34,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,1; 33,73</t>
+          <t>21,94; 32,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,29; 33,3</t>
+          <t>22,57; 33,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 34,53</t>
+          <t>23,63; 34,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,79; 24,52</t>
+          <t>15,87; 24,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,43; 27,33</t>
+          <t>20,28; 27,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,74; 30,34</t>
+          <t>23,65; 30,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,39; 26,94</t>
+          <t>20,09; 26,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,17; 70,28</t>
+          <t>14,27; 74,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,55; 43,81</t>
+          <t>31,47; 43,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,08; 41,17</t>
+          <t>31,07; 41,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,9; 36,43</t>
+          <t>26,98; 36,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,19; 30,87</t>
+          <t>22,8; 31,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,84; 30,81</t>
+          <t>24,6; 30,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,37; 32,66</t>
+          <t>27,33; 32,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,61; 29,11</t>
+          <t>23,76; 29,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,35; 66,72</t>
+          <t>18,47; 65,18</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17517; 34936</t>
+          <t>16905; 34507</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36778; 60835</t>
+          <t>35938; 60320</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16535; 34453</t>
+          <t>15271; 34446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6727; 19682</t>
+          <t>6562; 19890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10162; 22665</t>
+          <t>9896; 21841</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20269; 37391</t>
+          <t>21082; 37432</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17146; 32334</t>
+          <t>16641; 31630</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5477; 14190</t>
+          <t>5701; 14126</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29769; 52514</t>
+          <t>31029; 53095</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60608; 91619</t>
+          <t>61528; 92236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37351; 59427</t>
+          <t>36887; 61646</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14822; 31024</t>
+          <t>14764; 30600</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35608; 60129</t>
+          <t>35516; 59822</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54868; 85809</t>
+          <t>55772; 84468</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35324; 62939</t>
+          <t>35231; 59625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53655; 366474</t>
+          <t>55341; 368250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18194; 35702</t>
+          <t>18196; 34748</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32800; 52205</t>
+          <t>31947; 51709</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22136; 40550</t>
+          <t>22585; 41759</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19606; 33370</t>
+          <t>19368; 33440</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57315; 87420</t>
+          <t>58069; 88946</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92777; 127260</t>
+          <t>92694; 129843</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62864; 94342</t>
+          <t>63051; 93469</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94119; 417582</t>
+          <t>95026; 421061</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26338; 47168</t>
+          <t>26271; 47385</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38109; 63049</t>
+          <t>38516; 64095</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29023; 50857</t>
+          <t>29591; 53037</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15589; 37005</t>
+          <t>16618; 37781</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12822; 25072</t>
+          <t>13123; 25831</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29987; 51844</t>
+          <t>29829; 51031</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13844; 29991</t>
+          <t>14311; 30322</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13259; 28207</t>
+          <t>12185; 26863</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42446; 68272</t>
+          <t>44339; 67787</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75064; 107946</t>
+          <t>75813; 108167</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47158; 76862</t>
+          <t>48230; 75809</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33131; 58505</t>
+          <t>32625; 57467</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27793; 48091</t>
+          <t>27176; 47348</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42516; 69472</t>
+          <t>43371; 69066</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39493; 64854</t>
+          <t>40127; 64529</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23315; 42671</t>
+          <t>22194; 43153</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24391; 42281</t>
+          <t>24610; 42796</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22811; 42450</t>
+          <t>22406; 43221</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32590; 55761</t>
+          <t>33388; 55794</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24538; 43025</t>
+          <t>24782; 43705</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57090; 87150</t>
+          <t>56688; 84900</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70546; 105395</t>
+          <t>71437; 104453</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79190; 114935</t>
+          <t>78650; 113409</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50140; 77869</t>
+          <t>50392; 78815</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>125205; 167489</t>
+          <t>124287; 166633</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>196522; 251189</t>
+          <t>195806; 249507</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>141854; 187411</t>
+          <t>139744; 186942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119283; 591810</t>
+          <t>120136; 630142</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>78394; 108845</t>
+          <t>78185; 108434</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>121547; 161016</t>
+          <t>121524; 162416</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>102930; 139379</t>
+          <t>103228; 140116</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>73655; 102448</t>
+          <t>75678; 105035</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>213945; 265436</t>
+          <t>211891; 265948</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>333682; 398064</t>
+          <t>333130; 396541</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>254596; 313914</t>
+          <t>256191; 312961</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>215406; 783181</t>
+          <t>216793; 765163</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q25_A_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,25; 27,04</t>
+          <t>13,7; 27,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,6; 31,22</t>
+          <t>18,68; 31,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,26; 25,4</t>
+          <t>11,86; 25,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 17,51</t>
+          <t>6,49; 17,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,82; 52,58</t>
+          <t>24,93; 52,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,67; 50,9</t>
+          <t>28,42; 51,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,23; 49,86</t>
+          <t>25,06; 50,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,7; 29,0</t>
+          <t>11,25; 29,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,34; 31,39</t>
+          <t>18,62; 31,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,06; 34,58</t>
+          <t>23,68; 34,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,53; 30,97</t>
+          <t>18,39; 31,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,1; 18,86</t>
+          <t>9,04; 19,18</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,23; 32,39</t>
+          <t>19,08; 33,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,73; 32,91</t>
+          <t>21,71; 32,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 27,62</t>
+          <t>16,17; 27,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,91; 92,57</t>
+          <t>10,71; 21,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,28; 44,45</t>
+          <t>22,94; 44,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,49; 52,59</t>
+          <t>30,86; 53,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,77; 40,24</t>
+          <t>21,65; 38,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,86; 41,19</t>
+          <t>24,14; 41,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 33,84</t>
+          <t>22,19; 33,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,11; 36,58</t>
+          <t>26,24; 36,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,73; 29,25</t>
+          <t>19,93; 29,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,84; 87,91</t>
+          <t>16,84; 26,35</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,0; 36,07</t>
+          <t>20,14; 35,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,2; 36,94</t>
+          <t>22,11; 37,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,48; 36,7</t>
+          <t>20,6; 35,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 26,84</t>
+          <t>11,13; 25,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,07; 65,09</t>
+          <t>32,35; 61,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,81; 47,59</t>
+          <t>28,36; 49,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 36,9</t>
+          <t>17,34; 37,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,4; 36,16</t>
+          <t>17,79; 37,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,92; 39,63</t>
+          <t>25,71; 40,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,01; 38,53</t>
+          <t>27,06; 38,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,28; 33,44</t>
+          <t>21,95; 33,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 26,72</t>
+          <t>15,43; 26,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 27,97</t>
+          <t>16,71; 29,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,21; 33,78</t>
+          <t>20,34; 33,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,1; 32,32</t>
+          <t>20,05; 32,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 22,73</t>
+          <t>12,41; 23,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,63; 48,04</t>
+          <t>26,94; 47,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 38,58</t>
+          <t>19,71; 38,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,05; 41,87</t>
+          <t>24,86; 42,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,4; 34,22</t>
+          <t>19,83; 34,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,94; 32,86</t>
+          <t>21,91; 32,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,57; 33,01</t>
+          <t>21,94; 32,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,63; 34,07</t>
+          <t>23,84; 34,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,87; 24,82</t>
+          <t>16,8; 25,56</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,28; 27,19</t>
+          <t>20,69; 27,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,65; 30,14</t>
+          <t>23,85; 30,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,09; 26,88</t>
+          <t>20,46; 26,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,27; 74,84</t>
+          <t>12,74; 18,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,47; 43,64</t>
+          <t>31,96; 44,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,07; 41,53</t>
+          <t>31,47; 41,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,98; 36,62</t>
+          <t>26,9; 36,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,8; 31,65</t>
+          <t>23,0; 31,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,6; 30,87</t>
+          <t>24,84; 30,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,33; 32,53</t>
+          <t>27,45; 33,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,76; 29,03</t>
+          <t>23,52; 29,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 65,18</t>
+          <t>17,13; 22,23</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>22870</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16905; 34507</t>
+          <t>17483; 34460</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35938; 60320</t>
+          <t>36104; 59923</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15271; 34446</t>
+          <t>16080; 34612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6562; 19890</t>
+          <t>7910; 21366</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9896; 21841</t>
+          <t>10357; 21724</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21082; 37432</t>
+          <t>20902; 37960</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16641; 31630</t>
+          <t>15897; 31806</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5701; 14126</t>
+          <t>5887; 15563</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31029; 53095</t>
+          <t>31506; 52780</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61528; 92236</t>
+          <t>63168; 91811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36887; 61646</t>
+          <t>36593; 61915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14764; 30600</t>
+          <t>15743; 33411</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>268155</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26197</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>294352</t>
+          <t>54879</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35516; 59822</t>
+          <t>35243; 61785</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55772; 84468</t>
+          <t>55715; 84232</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35231; 59625</t>
+          <t>34902; 60095</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55341; 368250</t>
+          <t>18200; 37250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18196; 34748</t>
+          <t>17932; 34602</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31947; 51709</t>
+          <t>30341; 52188</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22585; 41759</t>
+          <t>22466; 40458</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19368; 33440</t>
+          <t>21169; 36669</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58069; 88946</t>
+          <t>58321; 88139</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92694; 129843</t>
+          <t>93150; 130415</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63051; 93469</t>
+          <t>63712; 94584</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>95026; 421061</t>
+          <t>43375; 67887</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>28696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19345</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44030</t>
+          <t>50600</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26271; 47385</t>
+          <t>26455; 46973</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38516; 64095</t>
+          <t>38362; 65356</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29591; 53037</t>
+          <t>29765; 52018</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16618; 37781</t>
+          <t>18233; 42338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13123; 25831</t>
+          <t>12836; 24538</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29829; 51031</t>
+          <t>30416; 52959</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14311; 30322</t>
+          <t>14247; 30550</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12185; 26863</t>
+          <t>14771; 31185</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44339; 67787</t>
+          <t>43979; 69077</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75813; 108167</t>
+          <t>75967; 108330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48230; 75809</t>
+          <t>49752; 75970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32625; 57467</t>
+          <t>38082; 66103</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31389</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>36504</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63808</t>
+          <t>69835</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27176; 47348</t>
+          <t>28277; 50056</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43371; 69066</t>
+          <t>41592; 68274</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40127; 64529</t>
+          <t>40022; 65443</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22194; 43153</t>
+          <t>24513; 46325</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24610; 42796</t>
+          <t>24000; 42083</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22406; 43221</t>
+          <t>22078; 42570</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33388; 55794</t>
+          <t>33132; 56686</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24782; 43705</t>
+          <t>27138; 47335</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56688; 84900</t>
+          <t>56603; 84397</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71437; 104453</t>
+          <t>69440; 103427</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78650; 113409</t>
+          <t>79364; 114306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50392; 78815</t>
+          <t>56187; 85471</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336115</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>87565</t>
+          <t>96772</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>423679</t>
+          <t>198185</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>124287; 166633</t>
+          <t>126793; 168183</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>195806; 249507</t>
+          <t>197477; 249396</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139744; 186942</t>
+          <t>142331; 187264</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120136; 630142</t>
+          <t>83236; 122653</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>78185; 108434</t>
+          <t>79418; 109802</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>121524; 162416</t>
+          <t>123096; 161109</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>103228; 140116</t>
+          <t>102934; 138426</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>75678; 105035</t>
+          <t>82780; 113518</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>211891; 265948</t>
+          <t>213966; 266848</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>333130; 396541</t>
+          <t>334545; 403641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>256191; 312961</t>
+          <t>253555; 313815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>216793; 765163</t>
+          <t>173504; 225223</t>
         </is>
       </c>
     </row>
